--- a/research/traditional_assets/database/data/lithuania/lithuania_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/lithuania/lithuania_bank_money_center.xlsx
@@ -588,10 +588,10 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0433</v>
+        <v>0.111</v>
       </c>
       <c r="E2">
-        <v>0.0398</v>
+        <v>0.132</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -606,85 +606,85 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>61.4</v>
+        <v>57</v>
       </c>
       <c r="L2">
-        <v>0.4401433691756272</v>
+        <v>0.4505928853754941</v>
       </c>
       <c r="M2">
-        <v>3.92</v>
+        <v>20.691</v>
       </c>
       <c r="N2">
-        <v>0.00758220502901354</v>
+        <v>0.04698228882833787</v>
       </c>
       <c r="O2">
-        <v>0.06384364820846905</v>
+        <v>0.363</v>
       </c>
       <c r="P2">
-        <v>3.92</v>
+        <v>19.9</v>
       </c>
       <c r="Q2">
-        <v>0.00758220502901354</v>
+        <v>0.04518619436875568</v>
       </c>
       <c r="R2">
-        <v>0.06384364820846905</v>
+        <v>0.3491228070175438</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>0.7910000000000004</v>
       </c>
       <c r="T2">
-        <v>0</v>
+        <v>0.03822918176985165</v>
       </c>
       <c r="U2">
-        <v>986.3</v>
+        <v>301.5</v>
       </c>
       <c r="V2">
-        <v>1.907736943907157</v>
+        <v>0.6846049046321526</v>
       </c>
       <c r="W2">
-        <v>0.1510826771653543</v>
+        <v>0.1242100675528438</v>
       </c>
       <c r="X2">
-        <v>0.08320150002393814</v>
+        <v>0.1196788589188986</v>
       </c>
       <c r="Y2">
-        <v>0.0678811771414162</v>
+        <v>0.004531208633945169</v>
       </c>
       <c r="Z2">
-        <v>0.5027027027027026</v>
+        <v>0.4042825183764783</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.04777426404125841</v>
+        <v>0.07485462891313426</v>
       </c>
       <c r="AC2">
-        <v>-0.04777426404125841</v>
+        <v>-0.07485462891313426</v>
       </c>
       <c r="AD2">
-        <v>840.3</v>
+        <v>763.7</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>840.3</v>
+        <v>763.7</v>
       </c>
       <c r="AG2">
-        <v>-146</v>
+        <v>462.2</v>
       </c>
       <c r="AH2">
-        <v>0.6190967361673911</v>
+        <v>0.6342496470392825</v>
       </c>
       <c r="AI2">
-        <v>0.6467826354679803</v>
+        <v>0.6466553767993226</v>
       </c>
       <c r="AJ2">
-        <v>-0.3935309973045822</v>
+        <v>0.5120762242410813</v>
       </c>
       <c r="AK2">
-        <v>-0.4666027484819432</v>
+        <v>0.5255258669698692</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0433</v>
+        <v>0.111</v>
       </c>
       <c r="E3">
-        <v>0.0398</v>
+        <v>0.132</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -728,85 +728,85 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>61.4</v>
+        <v>57</v>
       </c>
       <c r="L3">
-        <v>0.4401433691756272</v>
+        <v>0.4505928853754941</v>
       </c>
       <c r="M3">
-        <v>3.92</v>
+        <v>20.691</v>
       </c>
       <c r="N3">
-        <v>0.00758220502901354</v>
+        <v>0.04698228882833787</v>
       </c>
       <c r="O3">
-        <v>0.06384364820846905</v>
+        <v>0.363</v>
       </c>
       <c r="P3">
-        <v>3.92</v>
+        <v>19.9</v>
       </c>
       <c r="Q3">
-        <v>0.00758220502901354</v>
+        <v>0.04518619436875568</v>
       </c>
       <c r="R3">
-        <v>0.06384364820846905</v>
+        <v>0.3491228070175438</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>0.7910000000000004</v>
       </c>
       <c r="T3">
-        <v>0</v>
+        <v>0.03822918176985165</v>
       </c>
       <c r="U3">
-        <v>986.3</v>
+        <v>301.5</v>
       </c>
       <c r="V3">
-        <v>1.907736943907157</v>
+        <v>0.6846049046321526</v>
       </c>
       <c r="W3">
-        <v>0.1510826771653543</v>
+        <v>0.1242100675528438</v>
       </c>
       <c r="X3">
-        <v>0.08320150002393814</v>
+        <v>0.1196788589188986</v>
       </c>
       <c r="Y3">
-        <v>0.0678811771414162</v>
+        <v>0.004531208633945169</v>
       </c>
       <c r="Z3">
-        <v>0.5027027027027026</v>
+        <v>0.4042825183764783</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.04777426404125841</v>
+        <v>0.07485462891313426</v>
       </c>
       <c r="AC3">
-        <v>-0.04777426404125841</v>
+        <v>-0.07485462891313426</v>
       </c>
       <c r="AD3">
-        <v>840.3</v>
+        <v>763.7</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>840.3</v>
+        <v>763.7</v>
       </c>
       <c r="AG3">
-        <v>-146</v>
+        <v>462.2</v>
       </c>
       <c r="AH3">
-        <v>0.6190967361673911</v>
+        <v>0.6342496470392825</v>
       </c>
       <c r="AI3">
-        <v>0.6467826354679803</v>
+        <v>0.6466553767993226</v>
       </c>
       <c r="AJ3">
-        <v>-0.3935309973045822</v>
+        <v>0.5120762242410813</v>
       </c>
       <c r="AK3">
-        <v>-0.4666027484819432</v>
+        <v>0.5255258669698692</v>
       </c>
       <c r="AL3">
         <v>0</v>

--- a/research/traditional_assets/database/data/lithuania/lithuania_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/lithuania/lithuania_bank_money_center.xlsx
@@ -588,10 +588,10 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.111</v>
+        <v>0.133</v>
       </c>
       <c r="E2">
-        <v>0.132</v>
+        <v>0.115</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -606,85 +606,85 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>57</v>
+        <v>84</v>
       </c>
       <c r="L2">
-        <v>0.4505928853754941</v>
+        <v>0.449678800856531</v>
       </c>
       <c r="M2">
-        <v>20.691</v>
+        <v>18.78</v>
       </c>
       <c r="N2">
-        <v>0.04698228882833787</v>
+        <v>0.04080834419817471</v>
       </c>
       <c r="O2">
-        <v>0.363</v>
+        <v>0.2235714285714286</v>
       </c>
       <c r="P2">
-        <v>19.9</v>
+        <v>16.8</v>
       </c>
       <c r="Q2">
-        <v>0.04518619436875568</v>
+        <v>0.03650586701434159</v>
       </c>
       <c r="R2">
-        <v>0.3491228070175438</v>
+        <v>0.2</v>
       </c>
       <c r="S2">
-        <v>0.7910000000000004</v>
+        <v>1.98</v>
       </c>
       <c r="T2">
-        <v>0.03822918176985165</v>
+        <v>0.1054313099041534</v>
       </c>
       <c r="U2">
-        <v>301.5</v>
+        <v>605.9</v>
       </c>
       <c r="V2">
-        <v>0.6846049046321526</v>
+        <v>1.316601477618427</v>
       </c>
       <c r="W2">
-        <v>0.1242100675528438</v>
+        <v>0.201294033069734</v>
       </c>
       <c r="X2">
-        <v>0.1196788589188986</v>
+        <v>0.09802121923214649</v>
       </c>
       <c r="Y2">
-        <v>0.004531208633945169</v>
+        <v>0.1032728138375875</v>
       </c>
       <c r="Z2">
-        <v>0.4042825183764783</v>
+        <v>0.2123934053439454</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.07485462891313426</v>
+        <v>0.06429776709046175</v>
       </c>
       <c r="AC2">
-        <v>-0.07485462891313426</v>
+        <v>-0.06429776709046175</v>
       </c>
       <c r="AD2">
-        <v>763.7</v>
+        <v>853.9</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>763.7</v>
+        <v>853.9</v>
       </c>
       <c r="AG2">
-        <v>462.2</v>
+        <v>248</v>
       </c>
       <c r="AH2">
-        <v>0.6342496470392825</v>
+        <v>0.6497983410699338</v>
       </c>
       <c r="AI2">
-        <v>0.6466553767993226</v>
+        <v>0.6205668604651162</v>
       </c>
       <c r="AJ2">
-        <v>0.5120762242410813</v>
+        <v>0.3501835639649816</v>
       </c>
       <c r="AK2">
-        <v>0.5255258669698692</v>
+        <v>0.3220360992078951</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.111</v>
+        <v>0.133</v>
       </c>
       <c r="E3">
-        <v>0.132</v>
+        <v>0.115</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -728,85 +728,85 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>57</v>
+        <v>84</v>
       </c>
       <c r="L3">
-        <v>0.4505928853754941</v>
+        <v>0.449678800856531</v>
       </c>
       <c r="M3">
-        <v>20.691</v>
+        <v>18.78</v>
       </c>
       <c r="N3">
-        <v>0.04698228882833787</v>
+        <v>0.04080834419817471</v>
       </c>
       <c r="O3">
-        <v>0.363</v>
+        <v>0.2235714285714286</v>
       </c>
       <c r="P3">
-        <v>19.9</v>
+        <v>16.8</v>
       </c>
       <c r="Q3">
-        <v>0.04518619436875568</v>
+        <v>0.03650586701434159</v>
       </c>
       <c r="R3">
-        <v>0.3491228070175438</v>
+        <v>0.2</v>
       </c>
       <c r="S3">
-        <v>0.7910000000000004</v>
+        <v>1.98</v>
       </c>
       <c r="T3">
-        <v>0.03822918176985165</v>
+        <v>0.1054313099041534</v>
       </c>
       <c r="U3">
-        <v>301.5</v>
+        <v>605.9</v>
       </c>
       <c r="V3">
-        <v>0.6846049046321526</v>
+        <v>1.316601477618427</v>
       </c>
       <c r="W3">
-        <v>0.1242100675528438</v>
+        <v>0.201294033069734</v>
       </c>
       <c r="X3">
-        <v>0.1196788589188986</v>
+        <v>0.09802121923214649</v>
       </c>
       <c r="Y3">
-        <v>0.004531208633945169</v>
+        <v>0.1032728138375875</v>
       </c>
       <c r="Z3">
-        <v>0.4042825183764783</v>
+        <v>0.2123934053439454</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.07485462891313426</v>
+        <v>0.06429776709046175</v>
       </c>
       <c r="AC3">
-        <v>-0.07485462891313426</v>
+        <v>-0.06429776709046175</v>
       </c>
       <c r="AD3">
-        <v>763.7</v>
+        <v>853.9</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>763.7</v>
+        <v>853.9</v>
       </c>
       <c r="AG3">
-        <v>462.2</v>
+        <v>248</v>
       </c>
       <c r="AH3">
-        <v>0.6342496470392825</v>
+        <v>0.6497983410699338</v>
       </c>
       <c r="AI3">
-        <v>0.6466553767993226</v>
+        <v>0.6205668604651162</v>
       </c>
       <c r="AJ3">
-        <v>0.5120762242410813</v>
+        <v>0.3501835639649816</v>
       </c>
       <c r="AK3">
-        <v>0.5255258669698692</v>
+        <v>0.3220360992078951</v>
       </c>
       <c r="AL3">
         <v>0</v>
